--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][Raw]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9785863757133484</v>
+        <v>0.9778296947479248</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8557231426239014</v>
+        <v>0.8527448773384094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9729499816894531</v>
+        <v>0.9493704438209534</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8677610158920288</v>
+        <v>0.4797795116901398</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9236301183700562</v>
+        <v>0.9279056787490845</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06201467663049698</v>
+        <v>0.08753110468387604</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9518161416053772</v>
+        <v>0.9445744752883911</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4858717024326324</v>
+        <v>0.4088633060455322</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9719749689102173</v>
+        <v>0.9738253355026245</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6954131126403809</v>
+        <v>0.7610645294189453</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9126268029212952</v>
+        <v>0.8965919017791748</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1108034923672676</v>
+        <v>0.07089473307132721</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9663734436035156</v>
+        <v>0.970297634601593</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5551793575286865</v>
+        <v>0.6743428111076355</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8706846237182617</v>
+        <v>0.8490915894508362</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02252955548465252</v>
+        <v>0.01321172993630171</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,27 +642,27 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9407709240913391</v>
+        <v>0.910647988319397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1542248278856277</v>
+        <v>0.03643094375729561</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.921836793422699</v>
+        <v>0.9236618280410767</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1586213409900665</v>
+        <v>0.193156510591507</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9768523573875427</v>
+        <v>0.9727756381034851</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8165050745010376</v>
+        <v>0.7355091571807861</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9112735986709595</v>
+        <v>0.9051041603088379</v>
       </c>
       <c r="I7" t="n">
-        <v>0.105118490755558</v>
+        <v>0.0970514714717865</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9738644361495972</v>
+        <v>0.961093544960022</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7434269785881042</v>
+        <v>0.4607883989810944</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.967110276222229</v>
+        <v>0.9538354873657227</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7661013007164001</v>
+        <v>0.5527723431587219</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.884010910987854</v>
+        <v>0.8840795159339905</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008369669318199158</v>
+        <v>0.01004987023770809</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9574782848358154</v>
+        <v>0.9495305418968201</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5846735835075378</v>
+        <v>0.4822860956192017</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9532848000526428</v>
+        <v>0.9594657421112061</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2969151437282562</v>
+        <v>0.427782416343689</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9480987787246704</v>
+        <v>0.9452661871910095</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4271537065505981</v>
+        <v>0.4185811281204224</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9416971802711487</v>
+        <v>0.9453351497650146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1620027720928192</v>
+        <v>0.2142323851585388</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8696517944335938</v>
+        <v>0.8760833144187927</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02169348858296871</v>
+        <v>0.03373581543564796</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9237865209579468</v>
+        <v>0.9260852932929993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0625285804271698</v>
+        <v>0.07971958816051483</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9764220118522644</v>
+        <v>0.9733253717422485</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9177073240280151</v>
+        <v>0.8891666531562805</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>0.89731365442276</v>
+        <v>0.8986642360687256</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01604212448000908</v>
+        <v>0.02016706578433514</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9632630944252014</v>
+        <v>0.9607111811637878</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6933869123458862</v>
+        <v>0.6747221350669861</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -934,16 +946,16 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9607124328613281</v>
+        <v>0.9589895606040955</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4288471341133118</v>
+        <v>0.4184605479240417</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8711463212966919</v>
+        <v>0.8760521411895752</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02291425690054893</v>
+        <v>0.03369840979576111</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8737326860427856</v>
+        <v>0.8652989864349365</v>
       </c>
       <c r="F15" t="n">
-        <v>0.005144694820046425</v>
+        <v>0.004261233378201723</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.922627866268158</v>
+        <v>0.9131031632423401</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1635788679122925</v>
+        <v>0.1305840909481049</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9714187383651733</v>
+        <v>0.9770262241363525</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6812083721160889</v>
+        <v>0.8353922963142395</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9573085904121399</v>
+        <v>0.9473276138305664</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5815740823745728</v>
+        <v>0.4485706686973572</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9595522284507751</v>
+        <v>0.9593952298164368</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4056279361248016</v>
+        <v>0.4263928830623627</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.9870973229408264</v>
+        <v>0.9807854294776917</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9952296018600464</v>
+        <v>0.9695123434066772</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.863664984703064</v>
+        <v>0.8696551322937012</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003236836986616254</v>
+        <v>0.005179506726562977</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9546456336975098</v>
+        <v>0.9516029357910156</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5339720249176025</v>
+        <v>0.5155003666877747</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9456046223640442</v>
+        <v>0.9529843926429749</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1992095857858658</v>
+        <v>0.3140282034873962</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1141,10 +1153,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8524256944656372</v>
+        <v>0.8497722744941711</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01168034598231316</v>
+        <v>0.01351960375905037</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9384891986846924</v>
+        <v>0.9429938197135925</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1365933269262314</v>
+        <v>0.1901525408029556</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9313603639602661</v>
+        <v>0.9396120309829712</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2293337285518646</v>
+        <v>0.3442883193492889</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9541193246841431</v>
+        <v>0.9634473919868469</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3097899258136749</v>
+        <v>0.5114872455596924</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,14 +1229,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8822720646858215</v>
+        <v>0.8914031982421875</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03461652249097824</v>
+        <v>0.05862720310688019</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9323604702949524</v>
+        <v>0.9318681955337524</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09853978455066681</v>
+        <v>0.1073306798934937</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8785372376441956</v>
+        <v>0.8548879623413086</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03011023998260498</v>
+        <v>0.01609122753143311</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9814724922180176</v>
+        <v>0.9782091975212097</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9126490950584412</v>
+        <v>0.8607035279273987</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.937699556350708</v>
+        <v>0.921051561832428</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2919122278690338</v>
+        <v>0.1753833293914795</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9678332209587097</v>
+        <v>0.9592159986495972</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5907532572746277</v>
+        <v>0.4228749871253967</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.9427072405815125</v>
+        <v>0.9351652860641479</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3517092764377594</v>
+        <v>0.2939404249191284</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9563503861427307</v>
+        <v>0.953449010848999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3465912044048309</v>
+        <v>0.3212462961673737</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.929555356502533</v>
+        <v>0.91508549451828</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2139457017183304</v>
+        <v>0.140561655163765</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7877089977264404</v>
+        <v>0.7844235897064209</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0001427851966582239</v>
+        <v>0.0001656699314480647</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,10 +1419,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.9183670878410339</v>
+        <v>0.9216058254241943</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1385729610919952</v>
+        <v>0.1790190637111664</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9513335227966309</v>
+        <v>0.9489870071411133</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2686353027820587</v>
+        <v>0.2575726807117462</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8674618601799011</v>
+        <v>0.8734623789787292</v>
       </c>
       <c r="I27" t="n">
-        <v>0.02002704329788685</v>
+        <v>0.03073558583855629</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.985076904296875</v>
+        <v>0.9864574074745178</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9640313386917114</v>
+        <v>0.9799791574478149</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.9149408340454102</v>
+        <v>0.9184626340866089</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1212540045380592</v>
+        <v>0.1593359261751175</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9528931379318237</v>
+        <v>0.9385263919830322</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2910350561141968</v>
+        <v>0.1512302458286285</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9371117949485779</v>
+        <v>0.9343004822731018</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2855158746242523</v>
+        <v>0.2849403619766235</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8929533958435059</v>
+        <v>0.8941649198532104</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01292795967310667</v>
+        <v>0.01622231677174568</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.9332754015922546</v>
+        <v>0.9134418368339539</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2467931061983109</v>
+        <v>0.1322370767593384</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9442814588546753</v>
+        <v>0.9610426425933838</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1857733875513077</v>
+        <v>0.4597291648387909</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8790642619132996</v>
+        <v>0.8863039612770081</v>
       </c>
       <c r="I31" t="n">
-        <v>0.03070683777332306</v>
+        <v>0.04870480298995972</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9123870134353638</v>
+        <v>0.9159531593322754</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03446825593709946</v>
+        <v>0.04756955429911613</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.9659827947616577</v>
+        <v>0.9638720750808716</v>
       </c>
       <c r="I32" t="n">
-        <v>0.745005190372467</v>
+        <v>0.7322337627410889</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>0.927201509475708</v>
+        <v>0.9240134954452515</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0749092623591423</v>
+        <v>0.07168912142515182</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,14 +1685,14 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.8946975469589233</v>
+        <v>0.8814200758934021</v>
       </c>
       <c r="I33" t="n">
-        <v>0.05541541427373886</v>
+        <v>0.04083465039730072</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9655743837356567</v>
+        <v>0.9617993235588074</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5361536741256714</v>
+        <v>0.4756307005882263</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9467065334320068</v>
+        <v>0.9412983059883118</v>
       </c>
       <c r="I34" t="n">
-        <v>0.406556099653244</v>
+        <v>0.3652226328849792</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9659513831138611</v>
+        <v>0.9669398069381714</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5450872182846069</v>
+        <v>0.5923352241516113</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9206683039665222</v>
+        <v>0.9073734283447266</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1515682190656662</v>
+        <v>0.105565182864666</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9655793905258179</v>
+        <v>0.9687581062316895</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5362718105316162</v>
+        <v>0.6364176869392395</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9578285813331604</v>
+        <v>0.9525335431098938</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5910940766334534</v>
+        <v>0.5308586955070496</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9620516300201416</v>
+        <v>0.9549611806869507</v>
       </c>
       <c r="F37" t="n">
-        <v>0.456834614276886</v>
+        <v>0.3457272350788116</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9305957555770874</v>
+        <v>0.9419101476669312</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2226919680833817</v>
+        <v>0.3730740249156952</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9586610198020935</v>
+        <v>0.9591062068939209</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3884511590003967</v>
+        <v>0.42072993516922</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.9447247385978699</v>
+        <v>0.9276812672615051</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3785766661167145</v>
+        <v>0.2239595055580139</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9858552217483521</v>
+        <v>0.9829208850860596</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9718697071075439</v>
+        <v>0.9429745078086853</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.9365528225898743</v>
+        <v>0.9419397115707397</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2795498967170715</v>
+        <v>0.3734564781188965</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9250900745391846</v>
+        <v>0.9267958402633667</v>
       </c>
       <c r="F40" t="n">
-        <v>0.06698599457740784</v>
+        <v>0.08268050849437714</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.9474713802337646</v>
+        <v>0.940294623374939</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4177760779857635</v>
+        <v>0.3526380360126495</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9395871758460999</v>
+        <v>0.9378026723861694</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1448147892951965</v>
+        <v>0.1457047909498215</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,14 +1989,14 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8814473152160645</v>
+        <v>0.8919060230255127</v>
       </c>
       <c r="I41" t="n">
-        <v>0.03356390446424484</v>
+        <v>0.05971334874629974</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9408477544784546</v>
+        <v>0.931806743144989</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1548555940389633</v>
+        <v>0.1069912239909172</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9025204181671143</v>
+        <v>0.9067269563674927</v>
       </c>
       <c r="I42" t="n">
-        <v>0.07485818862915039</v>
+        <v>0.1030652746558189</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9482936263084412</v>
+        <v>0.948611319065094</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2294043898582458</v>
+        <v>0.2527669370174408</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9483045339584351</v>
+        <v>0.9422410130500793</v>
       </c>
       <c r="I43" t="n">
-        <v>0.4302634298801422</v>
+        <v>0.37737637758255</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9617119431495667</v>
+        <v>0.9679522514343262</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4496169984340668</v>
+        <v>0.61675626039505</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9226322174072266</v>
+        <v>0.9264698028564453</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1636064350605011</v>
+        <v>0.2142137289047241</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9329937100410461</v>
+        <v>0.9243338108062744</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1019199267029762</v>
+        <v>0.07287448644638062</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.963186502456665</v>
+        <v>0.9616419076919556</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6919264197349548</v>
+        <v>0.6916760802268982</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9332461357116699</v>
+        <v>0.9291824698448181</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1032996848225594</v>
+        <v>0.09347070753574371</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9293330907821655</v>
+        <v>0.9388056397438049</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2121198326349258</v>
+        <v>0.3346412181854248</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9265626072883606</v>
+        <v>0.9230123162269592</v>
       </c>
       <c r="F47" t="n">
-        <v>0.07241544872522354</v>
+        <v>0.06811010837554932</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9441937804222107</v>
+        <v>0.9376456737518311</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3713476061820984</v>
+        <v>0.3211695551872253</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9345376491546631</v>
+        <v>0.9272071123123169</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1106585562229156</v>
+        <v>0.08444532006978989</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9674687385559082</v>
+        <v>0.9605868458747864</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7727468013763428</v>
+        <v>0.672458827495575</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,27 +2276,27 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9139255285263062</v>
+        <v>0.9192664623260498</v>
       </c>
       <c r="F49" t="n">
-        <v>0.03732417151331902</v>
+        <v>0.05626945570111275</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8657717704772949</v>
+        <v>0.8686726689338684</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01883357204496861</v>
+        <v>0.02595459669828415</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9688819050788879</v>
+        <v>0.9670152068138123</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6168588399887085</v>
+        <v>0.5941412448883057</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,14 +2331,14 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.8961403965950012</v>
+        <v>0.8816116452217102</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05856230109930038</v>
+        <v>0.0411168746650219</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9796290397644043</v>
+        <v>0.9774219393730164</v>
       </c>
       <c r="F51" t="n">
-        <v>0.877655029296875</v>
+        <v>0.8440201878547668</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.9331323504447937</v>
+        <v>0.9331777691841125</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2454475164413452</v>
+        <v>0.2736258804798126</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9431379437446594</v>
+        <v>0.9439454674720764</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1748663336038589</v>
+        <v>0.1996120363473892</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,14 +2407,14 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9038669466972351</v>
+        <v>0.8827488422393799</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07885773479938507</v>
+        <v>0.04283458739519119</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9072306156158447</v>
+        <v>0.911148726940155</v>
       </c>
       <c r="F53" t="n">
-        <v>0.02644968964159489</v>
+        <v>0.03735534846782684</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.927455723285675</v>
+        <v>0.9154310822486877</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1972811669111252</v>
+        <v>0.1423775851726532</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E54" t="n">
-        <v>0.958355724811554</v>
+        <v>0.9587880373001099</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3826988339424133</v>
+        <v>0.4145604968070984</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.9585233926773071</v>
+        <v>0.940571665763855</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6039131283760071</v>
+        <v>0.3560755848884583</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9291380047798157</v>
+        <v>0.9246333837509155</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0830172523856163</v>
+        <v>0.07400127500295639</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9427288174629211</v>
+        <v>0.9448442459106445</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3519884049892426</v>
+        <v>0.4126323759555817</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>0.8909426331520081</v>
+        <v>0.8978886008262634</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01171305496245623</v>
+        <v>0.01942094974219799</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9279779195785522</v>
+        <v>0.9348491430282593</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2013055980205536</v>
+        <v>0.2906211614608765</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9405966997146606</v>
+        <v>0.9447453022003174</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1528032124042511</v>
+        <v>0.2079069763422012</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9333772659301758</v>
+        <v>0.945688009262085</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2477554678916931</v>
+        <v>0.424593061208725</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9618551135063171</v>
+        <v>0.9572984576225281</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4526492655277252</v>
+        <v>0.386587381362915</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.8318269848823547</v>
+        <v>0.8305103778839111</v>
       </c>
       <c r="I58" t="n">
-        <v>0.005735037848353386</v>
+        <v>0.007131556514650583</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,27 +2656,27 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9182351231575012</v>
+        <v>0.9187619090080261</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04671097546815872</v>
+        <v>0.05484522879123688</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9347757697105408</v>
+        <v>0.9335915446281433</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2613255381584167</v>
+        <v>0.2777475416660309</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9560557007789612</v>
+        <v>0.9626141786575317</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3415282070636749</v>
+        <v>0.4931555390357971</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.970333456993103</v>
+        <v>0.9507660865783691</v>
       </c>
       <c r="I60" t="n">
-        <v>0.824265718460083</v>
+        <v>0.5019199848175049</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9607653617858887</v>
+        <v>0.9271528124809265</v>
       </c>
       <c r="F61" t="n">
-        <v>0.429929792881012</v>
+        <v>0.084210105240345</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9614274501800537</v>
+        <v>0.9558384418487549</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6584519147872925</v>
+        <v>0.5873650312423706</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8977876901626587</v>
+        <v>0.9006735682487488</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01642545685172081</v>
+        <v>0.02224343083798885</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.9311527013778687</v>
+        <v>0.9407238960266113</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2275115102529526</v>
+        <v>0.3579756617546082</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9650509357452393</v>
+        <v>0.9651901125907898</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5238826274871826</v>
+        <v>0.5510847568511963</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,10 +2825,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.9355534315109253</v>
+        <v>0.945447564125061</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2691636979579926</v>
+        <v>0.4211576581001282</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9435988068580627</v>
+        <v>0.9445579051971436</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1791856586933136</v>
+        <v>0.2059342265129089</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9475997686386108</v>
+        <v>0.9577375650405884</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4196823537349701</v>
+        <v>0.6209888458251953</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,16 +2884,16 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9430953860282898</v>
+        <v>0.9395413398742676</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1744723170995712</v>
+        <v>0.1593272835016251</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9539044499397278</v>
+        <v>0.9432790875434875</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5211072564125061</v>
+        <v>0.3911372721195221</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9561731815338135</v>
+        <v>0.9595852494239807</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3435386419296265</v>
+        <v>0.430146336555481</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9419606328010559</v>
+        <v>0.9530573487281799</v>
       </c>
       <c r="I66" t="n">
-        <v>0.3421774208545685</v>
+        <v>0.5396174192428589</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9542641043663025</v>
+        <v>0.9608080387115479</v>
       </c>
       <c r="F67" t="n">
-        <v>0.3120718598365784</v>
+        <v>0.4548742473125458</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.9160553812980652</v>
+        <v>0.9246904253959656</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1266359686851501</v>
+        <v>0.2006286084651947</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9382281899452209</v>
+        <v>0.9432123899459839</v>
       </c>
       <c r="F68" t="n">
-        <v>0.1347077488899231</v>
+        <v>0.1922865062952042</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9565651416778564</v>
+        <v>0.9590232372283936</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5680820941925049</v>
+        <v>0.6440996527671814</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>0.845632016658783</v>
+        <v>0.8478935956954956</v>
       </c>
       <c r="F69" t="n">
-        <v>0.001456768601201475</v>
+        <v>0.001998367020860314</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,14 +3053,14 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8889756202697754</v>
+        <v>0.9043635725975037</v>
       </c>
       <c r="I69" t="n">
-        <v>0.04456673562526703</v>
+        <v>0.09442675113677979</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9727779626846313</v>
+        <v>0.9795486927032471</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7158924341201782</v>
+        <v>0.8874043822288513</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.9444790482521057</v>
+        <v>0.9416319727897644</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3752175271511078</v>
+        <v>0.3694868981838226</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9603040814399719</v>
+        <v>0.9680477380752563</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4205653071403503</v>
+        <v>0.6190771460533142</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.844377875328064</v>
+        <v>0.8303402066230774</v>
       </c>
       <c r="I71" t="n">
-        <v>0.00881328247487545</v>
+        <v>0.007092168089002371</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9163305759429932</v>
+        <v>0.9109358191490173</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04229190573096275</v>
+        <v>0.03695939481258392</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.9183640480041504</v>
+        <v>0.9241520762443542</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1385566741228104</v>
+        <v>0.1966838836669922</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9319266080856323</v>
+        <v>0.9371956586837769</v>
       </c>
       <c r="F73" t="n">
-        <v>0.09628952294588089</v>
+        <v>0.1412239968776703</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9893819689750671</v>
+        <v>0.9863198399543762</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9985618591308594</v>
+        <v>0.994589626789093</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9571737051010132</v>
+        <v>0.9651970863342285</v>
       </c>
       <c r="F74" t="n">
-        <v>0.3610644936561584</v>
+        <v>0.5512474775314331</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9582056403160095</v>
+        <v>0.9593406319618225</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5980368852615356</v>
+        <v>0.6498380303382874</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9748607277870178</v>
+        <v>0.972195029258728</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7683420181274414</v>
+        <v>0.7212406992912292</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,10 +3281,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.915814995765686</v>
+        <v>0.9222526550292969</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1254552453756332</v>
+        <v>0.1833547949790955</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9810225367546082</v>
+        <v>0.9816314578056335</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9045959711074829</v>
+        <v>0.9239048361778259</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9488986134529114</v>
+        <v>0.9403298497200012</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4393360912799835</v>
+        <v>0.35307377576828</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9732659459114075</v>
+        <v>0.9700013995170593</v>
       </c>
       <c r="F77" t="n">
-        <v>0.7282939553260803</v>
+        <v>0.6670215129852295</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9175947904586792</v>
+        <v>0.892427384853363</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1344649642705917</v>
+        <v>0.06086145341396332</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,16 +3378,16 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9507869482040405</v>
+        <v>0.9427159428596497</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2611581087112427</v>
+        <v>0.1874724626541138</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.965786337852478</v>
+        <v>0.9583093523979187</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7413033246994019</v>
+        <v>0.6312381029129028</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,16 +3416,16 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9643083214759827</v>
+        <v>0.968606173992157</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5067492127418518</v>
+        <v>0.6326985359191895</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3421,10 +3433,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.7821034789085388</v>
+        <v>0.7686829566955566</v>
       </c>
       <c r="I79" t="n">
-        <v>0.001165031921118498</v>
+        <v>0.001076486078090966</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9080325365066528</v>
+        <v>0.9123628735542297</v>
       </c>
       <c r="F80" t="n">
-        <v>0.02755586989223957</v>
+        <v>0.03969970718026161</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9111493825912476</v>
+        <v>0.9185634255409241</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1046114936470985</v>
+        <v>0.1599328070878983</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E81" t="n">
-        <v>0.927148699760437</v>
+        <v>0.9324442148208618</v>
       </c>
       <c r="F81" t="n">
-        <v>0.07469987124204636</v>
+        <v>0.1105630919337273</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3497,10 +3509,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.8536109328269958</v>
+        <v>0.8487030863761902</v>
       </c>
       <c r="I81" t="n">
-        <v>0.01217999402433634</v>
+        <v>0.01303936634212732</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9530401825904846</v>
+        <v>0.9581313133239746</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2932307422161102</v>
+        <v>0.4020425379276276</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.7551401853561401</v>
+        <v>0.7414132952690125</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0005241603939794004</v>
+        <v>0.0005016059149056673</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8864168524742126</v>
+        <v>0.8769004344940186</v>
       </c>
       <c r="F83" t="n">
-        <v>0.009398463182151318</v>
+        <v>0.007202541455626488</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.8823341727256775</v>
+        <v>0.8821020722389221</v>
       </c>
       <c r="I83" t="n">
-        <v>0.03469713032245636</v>
+        <v>0.04184865951538086</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9229376912117004</v>
+        <v>0.917870819568634</v>
       </c>
       <c r="F84" t="n">
-        <v>0.05979108437895775</v>
+        <v>0.05241990461945534</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9098694324493408</v>
+        <v>0.9069973826408386</v>
       </c>
       <c r="I84" t="n">
-        <v>0.09953149408102036</v>
+        <v>0.1041035354137421</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9408876895904541</v>
+        <v>0.9448506832122803</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1551846414804459</v>
+        <v>0.2090240865945816</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.9023556709289551</v>
+        <v>0.9176979660987854</v>
       </c>
       <c r="I85" t="n">
-        <v>0.07438326627016068</v>
+        <v>0.1548787802457809</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3670,16 +3682,16 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>0.951088011264801</v>
+        <v>0.9363175630569458</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2652534544467926</v>
+        <v>0.1349814534187317</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3687,10 +3699,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.9196125268936157</v>
+        <v>0.9268282055854797</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1454625725746155</v>
+        <v>0.2170540988445282</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>0.8911923170089722</v>
+        <v>0.893372654914856</v>
       </c>
       <c r="F87" t="n">
-        <v>0.01185714919120073</v>
+        <v>0.01561636384576559</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9612306356430054</v>
+        <v>0.9670579433441162</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6547189950942993</v>
+        <v>0.7889950275421143</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9646149277687073</v>
+        <v>0.9594723582267761</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5137819647789001</v>
+        <v>0.4279140532016754</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.8737266063690186</v>
+        <v>0.8749906420707703</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02519538067281246</v>
+        <v>0.03244925662875175</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9543105363845825</v>
+        <v>0.9548839926719666</v>
       </c>
       <c r="F89" t="n">
-        <v>0.312807023525238</v>
+        <v>0.3444404006004333</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,14 +3813,14 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.8762882351875305</v>
+        <v>0.9040260314941406</v>
       </c>
       <c r="I89" t="n">
-        <v>0.02769769355654716</v>
+        <v>0.09325484186410904</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9510050415992737</v>
+        <v>0.9410725831985474</v>
       </c>
       <c r="F90" t="n">
-        <v>0.2641189396381378</v>
+        <v>0.1723499447107315</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.8306480050086975</v>
+        <v>0.8223554491996765</v>
       </c>
       <c r="I90" t="n">
-        <v>0.00551143242046237</v>
+        <v>0.005481029395014048</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9310260415077209</v>
+        <v>0.9226443767547607</v>
       </c>
       <c r="F91" t="n">
-        <v>0.09178342670202255</v>
+        <v>0.06684136390686035</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.954894483089447</v>
+        <v>0.9613915681838989</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5383313298225403</v>
+        <v>0.6871143579483032</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9574366211891174</v>
+        <v>0.957598865032196</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3657893538475037</v>
+        <v>0.3921068906784058</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,10 +3927,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.9292781949043274</v>
+        <v>0.9688201546669006</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2116711884737015</v>
+        <v>0.8191524147987366</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9495768547058105</v>
+        <v>0.9543694257736206</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2452746480703354</v>
+        <v>0.3359663486480713</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,10 +3965,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.95442795753479</v>
+        <v>0.9668101668357849</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5301747918128967</v>
+        <v>0.7846686840057373</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9361459612846375</v>
+        <v>0.9355742931365967</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1205620989203453</v>
+        <v>0.1299119740724564</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.9442858099937439</v>
+        <v>0.9400236010551453</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3725926578044891</v>
+        <v>0.349302738904953</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9653452038764954</v>
+        <v>0.9577776789665222</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5307621359825134</v>
+        <v>0.3954221904277802</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9440961480140686</v>
+        <v>0.9510208368301392</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3700309693813324</v>
+        <v>0.5060312151908875</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,27 +4062,27 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9212955236434937</v>
+        <v>0.914116382598877</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05483994632959366</v>
+        <v>0.04335889592766762</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.8994597792625427</v>
+        <v>0.9030814170837402</v>
       </c>
       <c r="I96" t="n">
-        <v>0.06652485579252243</v>
+        <v>0.09005286544561386</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9643457531929016</v>
+        <v>0.9638601541519165</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5076045989990234</v>
+        <v>0.5207169055938721</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,10 +4117,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.9477421045303345</v>
+        <v>0.9551568627357483</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4218036532402039</v>
+        <v>0.5754826068878174</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9404117465019226</v>
+        <v>0.9492338299751282</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1513077765703201</v>
+        <v>0.2607754468917847</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,10 +4155,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.8291401267051697</v>
+        <v>0.8080577850341797</v>
       </c>
       <c r="I98" t="n">
-        <v>0.005238882265985012</v>
+        <v>0.00349145382642746</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8895934224128723</v>
+        <v>0.8905850052833557</v>
       </c>
       <c r="F99" t="n">
-        <v>0.01096586231142282</v>
+        <v>0.01366690918803215</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.955473005771637</v>
+        <v>0.9545559287071228</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5485395789146423</v>
+        <v>0.5650995373725891</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9400643110275269</v>
+        <v>0.9491369128227234</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1485377103090286</v>
+        <v>0.2595134675502777</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.9197733402252197</v>
+        <v>0.9312888383865356</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1463766843080521</v>
+        <v>0.2555095851421356</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E101" t="n">
-        <v>0.942629873752594</v>
+        <v>0.9463620185852051</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1702208667993546</v>
+        <v>0.2256781458854675</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4257,10 +4269,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.898291289806366</v>
+        <v>0.9046611785888672</v>
       </c>
       <c r="I101" t="n">
-        <v>0.06360139697790146</v>
+        <v>0.09547267109155655</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D102" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9457315802574158</v>
+        <v>0.9512732625007629</v>
       </c>
       <c r="F102" t="n">
-        <v>0.2005462944507599</v>
+        <v>0.288642019033432</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.9585046172142029</v>
+        <v>0.9526374340057373</v>
       </c>
       <c r="I102" t="n">
-        <v>0.603564977645874</v>
+        <v>0.532589316368103</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9572893977165222</v>
+        <v>0.9575886726379395</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3631376028060913</v>
+        <v>0.3919186294078827</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.9730572700500488</v>
+        <v>0.976693332195282</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8694501519203186</v>
+        <v>0.9319134950637817</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4354,16 +4366,16 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9863949418067932</v>
+        <v>0.9857685565948486</v>
       </c>
       <c r="F104" t="n">
-        <v>0.9766240119934082</v>
+        <v>0.9745401740074158</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4371,10 +4383,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.8713799715042114</v>
+        <v>0.8748813271522522</v>
       </c>
       <c r="I104" t="n">
-        <v>0.02311155200004578</v>
+        <v>0.03232341259717941</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4392,16 +4404,16 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8773987889289856</v>
+        <v>0.859255850315094</v>
       </c>
       <c r="F105" t="n">
-        <v>0.006110156420618296</v>
+        <v>0.003262904938310385</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4409,10 +4421,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9045726656913757</v>
+        <v>0.9002646207809448</v>
       </c>
       <c r="I105" t="n">
-        <v>0.08104094117879868</v>
+        <v>0.08115681260824203</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9628885388374329</v>
+        <v>0.9625550508499146</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4749533236026764</v>
+        <v>0.4918705224990845</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,10 +4459,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.904349148273468</v>
+        <v>0.9007166624069214</v>
       </c>
       <c r="I106" t="n">
-        <v>0.08034282177686691</v>
+        <v>0.08252128958702087</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9469514489173889</v>
+        <v>0.9450055956840515</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2138321250677109</v>
+        <v>0.2106761783361435</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,10 +4497,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.9845733046531677</v>
+        <v>0.9844701290130615</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9873161315917969</v>
+        <v>0.9891777634620667</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8707190155982971</v>
+        <v>0.8767927885055542</v>
       </c>
       <c r="F108" t="n">
-        <v>0.004472262226045132</v>
+        <v>0.007167004514485598</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.9347221851348877</v>
+        <v>0.9281114935874939</v>
       </c>
       <c r="I108" t="n">
-        <v>0.260793149471283</v>
+        <v>0.2275205105543137</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9408704042434692</v>
+        <v>0.9499738216400146</v>
       </c>
       <c r="F109" t="n">
-        <v>0.155042439699173</v>
+        <v>0.2705937027931213</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.8165546655654907</v>
+        <v>0.8060252666473389</v>
       </c>
       <c r="I109" t="n">
-        <v>0.003452622098848224</v>
+        <v>0.003278137417510152</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E110" t="n">
-        <v>0.963738739490509</v>
+        <v>0.9650456309318542</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4938378930091858</v>
+        <v>0.5477423071861267</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9510554075241089</v>
+        <v>0.9559619426727295</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4734257459640503</v>
+        <v>0.5895295143127441</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,27 +4632,27 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8983301520347595</v>
+        <v>0.9193509817123413</v>
       </c>
       <c r="F111" t="n">
-        <v>0.01687596179544926</v>
+        <v>0.05651191994547844</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9680702090263367</v>
+        <v>0.9738906621932983</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7838129997253418</v>
+        <v>0.8970016241073608</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D112" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9684136509895325</v>
+        <v>0.9697720408439636</v>
       </c>
       <c r="F112" t="n">
-        <v>0.6051532030105591</v>
+        <v>0.661358118057251</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.8588864803314209</v>
+        <v>0.833149254322052</v>
       </c>
       <c r="I112" t="n">
-        <v>0.0146951312199235</v>
+        <v>0.007773067802190781</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9692274332046509</v>
+        <v>0.9623861312866211</v>
       </c>
       <c r="F113" t="n">
-        <v>0.625541627407074</v>
+        <v>0.4882099628448486</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,14 +4725,14 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.8872921466827393</v>
+        <v>0.8950002193450928</v>
       </c>
       <c r="I113" t="n">
-        <v>0.04181542247533798</v>
+        <v>0.06687196344137192</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9674010276794434</v>
+        <v>0.9719601273536682</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5801202654838562</v>
+        <v>0.7154513597488403</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,10 +4763,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.9330499768257141</v>
+        <v>0.9228469133377075</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2446752786636353</v>
+        <v>0.1874282509088516</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9685543179512024</v>
+        <v>0.9654018878936768</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6086617708206177</v>
+        <v>0.5560047030448914</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9478728771209717</v>
+        <v>0.9348382353782654</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4237598478794098</v>
+        <v>0.2905071079730988</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,16 +4822,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9022498726844788</v>
+        <v>0.8794388175010681</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02054352685809135</v>
+        <v>0.008096949197351933</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4827,10 +4839,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9207287430763245</v>
+        <v>0.9102556705474854</v>
       </c>
       <c r="I116" t="n">
-        <v>0.151925265789032</v>
+        <v>0.117480456829071</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9354369640350342</v>
+        <v>0.9374757409095764</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1160911619663239</v>
+        <v>0.1432742327451706</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.825115442276001</v>
+        <v>0.8132005333900452</v>
       </c>
       <c r="I117" t="n">
-        <v>0.004579274915158749</v>
+        <v>0.004100078716874123</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9480236768722534</v>
+        <v>0.938710629940033</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2261899560689926</v>
+        <v>0.1526696681976318</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,10 +4915,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9173094034194946</v>
+        <v>0.9217262268066406</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1329779177904129</v>
+        <v>0.1798186600208282</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4924,27 +4936,27 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9112715721130371</v>
+        <v>0.9191927313804626</v>
       </c>
       <c r="F119" t="n">
-        <v>0.03254075348377228</v>
+        <v>0.05605900287628174</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9641072154045105</v>
+        <v>0.96837317943573</v>
       </c>
       <c r="I119" t="n">
-        <v>0.7094669938087463</v>
+        <v>0.8116169571876526</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8819020390510559</v>
+        <v>0.886766791343689</v>
       </c>
       <c r="F120" t="n">
-        <v>0.00756574422121048</v>
+        <v>0.01140338368713856</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9155229330062866</v>
+        <v>0.9227262735366821</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1240356042981148</v>
+        <v>0.1865944713354111</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9650084376335144</v>
+        <v>0.9698939323425293</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5228930711746216</v>
+        <v>0.6643664240837097</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.9322078824043274</v>
+        <v>0.9239749312400818</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2369132190942764</v>
+        <v>0.1954023391008377</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
